--- a/Delhi-January-2026.xlsx
+++ b/Delhi-January-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="87">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Delhi</t>
   </si>
   <si>
@@ -118,10 +121,10 @@
     <t>HR38AE5738</t>
   </si>
   <si>
-    <t>HR55AR-0857</t>
-  </si>
-  <si>
-    <t>HR55AR-1793</t>
+    <t>HR55AR0857</t>
+  </si>
+  <si>
+    <t>HR55AR1793</t>
   </si>
   <si>
     <t>MH02FG4092</t>
@@ -142,13 +145,13 @@
     <t>HR55AU6270</t>
   </si>
   <si>
-    <t>MH02FG 4112</t>
-  </si>
-  <si>
-    <t>MH02FG 7817</t>
-  </si>
-  <si>
-    <t>MH02FG 0905</t>
+    <t>MH02FG4112</t>
+  </si>
+  <si>
+    <t>MH02FG7817</t>
+  </si>
+  <si>
+    <t>MH02FG0905</t>
   </si>
   <si>
     <t>MH02GH0253</t>
@@ -172,7 +175,7 @@
     <t>HR55AX5016</t>
   </si>
   <si>
-    <t>DL1N-6505</t>
+    <t>DL1N6505</t>
   </si>
   <si>
     <t>HR38AE9224</t>
@@ -205,7 +208,7 @@
     <t>BYD E6</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
@@ -235,28 +238,43 @@
     <t>21/04/2023</t>
   </si>
   <si>
+    <t>28/11/2023</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>21/09/2021</t>
+  </si>
+  <si>
+    <t>21/10/2021</t>
+  </si>
+  <si>
+    <t>28/06/2022</t>
+  </si>
+  <si>
+    <t>16/09/2024</t>
+  </si>
+  <si>
+    <t>30/05/2023</t>
+  </si>
+  <si>
+    <t>24/06/2025</t>
+  </si>
+  <si>
+    <t>21/04/2014</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>23/01/2025</t>
+  </si>
+  <si>
+    <t>30/07/2024</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>25/03/2021</t>
-  </si>
-  <si>
-    <t>21/09/2021</t>
-  </si>
-  <si>
-    <t>21/10/2021</t>
-  </si>
-  <si>
-    <t>30/05/2023</t>
-  </si>
-  <si>
-    <t>14/03/2023</t>
-  </si>
-  <si>
-    <t>23/01/2025</t>
-  </si>
-  <si>
-    <t>30/07/2024</t>
   </si>
 </sst>
 </file>
@@ -618,10 +636,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z35"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,28 +718,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2">
         <v>66412</v>
@@ -781,27 +802,27 @@
         <v>-29.87</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H3">
         <v>228021</v>
@@ -861,24 +882,24 @@
         <v>49.94</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>64</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="2">
         <v>44904</v>
@@ -941,27 +962,27 @@
         <v>31.89</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H5">
         <v>183323</v>
@@ -1021,24 +1042,24 @@
         <v>53.93</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6" s="2">
         <v>44904</v>
@@ -1101,27 +1122,27 @@
         <v>49.45</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>67</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2026</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7">
         <v>128344</v>
@@ -1181,27 +1202,27 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>68</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2026</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>111921</v>
@@ -1261,27 +1282,27 @@
         <v>11.23</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2026</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>130965</v>
@@ -1341,24 +1362,24 @@
         <v>-7.98</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G10" s="2">
         <v>44441</v>
@@ -1421,27 +1442,27 @@
         <v>37.38</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2026</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H11">
         <v>114209</v>
@@ -1501,27 +1522,27 @@
         <v>54.72</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2026</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>116775</v>
@@ -1581,27 +1602,27 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2026</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>107949</v>
@@ -1661,24 +1682,24 @@
         <v>30.98</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2026</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G14" s="2">
         <v>44629</v>
@@ -1741,24 +1762,24 @@
         <v>55.14</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2026</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15" s="2">
         <v>45331</v>
@@ -1821,27 +1842,27 @@
         <v>18.48</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2026</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16" t="s">
-        <v>73</v>
+        <v>64</v>
+      </c>
+      <c r="G16" s="2">
+        <v>44471</v>
       </c>
       <c r="H16">
         <v>82225</v>
@@ -1906,22 +1927,22 @@
         <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2026</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H17">
         <v>58904</v>
@@ -1986,22 +2007,22 @@
         <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2026</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H18">
         <v>15722</v>
@@ -2066,19 +2087,19 @@
         <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2026</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G19" s="2">
         <v>45634</v>
@@ -2146,22 +2167,22 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2026</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H20">
         <v>135531</v>
@@ -2226,22 +2247,22 @@
         <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2026</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H21">
         <v>14056</v>
@@ -2306,19 +2327,19 @@
         <v>82</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2026</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G22" s="2">
         <v>45083</v>
@@ -2386,19 +2407,19 @@
         <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2026</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G23" s="2">
         <v>45323</v>
@@ -2466,22 +2487,22 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2026</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H24">
         <v>24738</v>
@@ -2546,22 +2567,22 @@
         <v>85</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2026</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H25">
         <v>18636</v>
@@ -2626,22 +2647,22 @@
         <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2026</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2686,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="Z26" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -2694,22 +2715,22 @@
         <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2026</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H27">
         <v>109644</v>
@@ -2774,19 +2795,19 @@
         <v>88</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2026</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2">
         <v>45451</v>
@@ -2854,19 +2875,19 @@
         <v>89</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2026</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2">
         <v>45451</v>
@@ -2934,19 +2955,19 @@
         <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2026</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2">
         <v>45511</v>
@@ -3014,19 +3035,19 @@
         <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2026</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2">
         <v>45511</v>
@@ -3094,22 +3115,22 @@
         <v>92</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2026</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H32">
         <v>21913</v>
@@ -3174,22 +3195,22 @@
         <v>93</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2026</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H33">
         <v>92022</v>
@@ -3254,22 +3275,22 @@
         <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2026</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H34">
         <v>79275</v>
@@ -3334,22 +3355,22 @@
         <v>95</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2026</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H35">
         <v>75448</v>
